--- a/survey_templates/042_vote_for_your_favorite_bird--survey_templates.xlsx
+++ b/survey_templates/042_vote_for_your_favorite_bird--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (if above)</t>
+          <t>Time Of Day Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other (if above)</t>
+          <t>Favorite Bird Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other (if above)</t>
+          <t>How Did You Hear About Us Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media', 'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'google',_'label':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Google', 'label': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'event',_'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Event', 'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'word_of_mouth',_'label':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Word of Mouth', 'label': 'Word of Mouth'}</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
